--- a/data/RSS_link.xlsx
+++ b/data/RSS_link.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8779c4def3e22337/ドキュメント/GitHub/rss-daily-digest/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="70" documentId="11_AD4D066CA252ABDACC10489A1917CC5073EEDF52" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7AAC2839-ABF2-4346-96AE-14DCDB318DC5}"/>
+  <xr:revisionPtr revIDLastSave="80" documentId="11_AD4D066CA252ABDACC10489A1917CC5073EEDF52" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7B28BEAB-4DA9-46E0-886B-CB3DCCA784B0}"/>
   <bookViews>
-    <workbookView xWindow="1920" yWindow="1920" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,11 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="44">
-  <si>
-    <t>FRB</t>
-    <phoneticPr fontId="1"/>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="47">
   <si>
     <t>federalreserve.gov/feeds/press_all.xml</t>
   </si>
@@ -52,135 +48,152 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
+    <t>BIS2</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>bis.org/doclist/reshub_papers.rss</t>
+  </si>
+  <si>
+    <t>ecb.europa.eu/rss/press.html</t>
+  </si>
+  <si>
+    <t>ECB</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>EBA</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://eba.europa.eu/news-press/news/rss.xml</t>
+  </si>
+  <si>
+    <t>bankofengland.co.uk/rss/news</t>
+  </si>
+  <si>
+    <t>SRB</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>srb.europa.eu/en/rss</t>
+  </si>
+  <si>
+    <t>FSA</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>BOJ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>fsa.go.jp/fsaNewsListAll_rss2.xml</t>
+  </si>
+  <si>
+    <t>boj.or.jp/rss/whatsnew.xml</t>
+  </si>
+  <si>
+    <t>FINMA</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>HKMA</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>OSFI</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>finma.ch/en/rss/news/</t>
+  </si>
+  <si>
+    <t>RSS feed of HKMA: Press Releases</t>
+  </si>
+  <si>
+    <t>osfi-bsif.gc.ca/en/rss.xml</t>
+  </si>
+  <si>
+    <t>https://www.bis.org/doclist/all_pressrels.rss</t>
+  </si>
+  <si>
+    <t>https://www.bis.org/doclist/reshub_papers.rss</t>
+  </si>
+  <si>
+    <t>https://www.hkma.gov.hk/eng/other-information/rss/rss_press-release.xml</t>
+  </si>
+  <si>
+    <t>https://www.federalreserve.gov/feeds/press_all.xml</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://www.fsb.org/wordpress/content_type/press/feed/</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://www.occ.gov/rss/occ_news.xml</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://www.ecb.europa.eu/rss/press.html</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://www.srb.europa.eu/en/rss</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://www.fsa.go.jp/fsaNewsListAll_rss2.xml</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://www.boj.or.jp/rss/whatsnew.xml</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://www.finma.ch/en/rss/news/</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://www.osfi-bsif.gc.ca/en/rss.xml</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>BOE1</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>BOE2</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>bankofengland.co.uk/rss/publications</t>
+  </si>
+  <si>
+    <t>https://www.bankofengland.co.uk/rss/publications</t>
+  </si>
+  <si>
+    <t>https://www.bankofengland.co.uk/rss/news</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
     <t>bis.org/doclist/all_pressrels.rss</t>
-  </si>
-  <si>
-    <t>BIS2</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>bis.org/doclist/reshub_papers.rss</t>
-  </si>
-  <si>
-    <t>ecb.europa.eu/rss/press.html</t>
-  </si>
-  <si>
-    <t>ECB</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>EBA</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>https://eba.europa.eu/news-press/news/rss.xml</t>
-  </si>
-  <si>
-    <t>bankofengland.co.uk/rss/news</t>
-  </si>
-  <si>
-    <t>SRB</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>srb.europa.eu/en/rss</t>
-  </si>
-  <si>
-    <t>FSA</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>BOJ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>fsa.go.jp/fsaNewsListAll_rss2.xml</t>
-  </si>
-  <si>
-    <t>boj.or.jp/rss/whatsnew.xml</t>
-  </si>
-  <si>
-    <t>FINMA</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>HKMA</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>OSFI</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>finma.ch/en/rss/news/</t>
-  </si>
-  <si>
-    <t>RSS feed of HKMA: Press Releases</t>
-  </si>
-  <si>
-    <t>osfi-bsif.gc.ca/en/rss.xml</t>
-  </si>
-  <si>
-    <t>https://www.bis.org/doclist/all_pressrels.rss</t>
-  </si>
-  <si>
-    <t>https://www.bis.org/doclist/reshub_papers.rss</t>
-  </si>
-  <si>
-    <t>https://www.hkma.gov.hk/eng/other-information/rss/rss_press-release.xml</t>
-  </si>
-  <si>
-    <t>https://www.federalreserve.gov/feeds/press_all.xml</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>https://www.fsb.org/wordpress/content_type/press/feed/</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>https://www.occ.gov/rss/occ_news.xml</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>https://www.ecb.europa.eu/rss/press.html</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>https://www.srb.europa.eu/en/rss</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>https://www.fsa.go.jp/fsaNewsListAll_rss2.xml</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>https://www.boj.or.jp/rss/whatsnew.xml</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>https://www.finma.ch/en/rss/news/</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>https://www.osfi-bsif.gc.ca/en/rss.xml</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>BOE1</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>BOE2</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>bankofengland.co.uk/rss/publications</t>
-  </si>
-  <si>
-    <t>https://www.bankofengland.co.uk/rss/publications</t>
-  </si>
-  <si>
-    <t>https://www.bankofengland.co.uk/rss/news</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>FRB_press_all</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>FRB_bankinginfo</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>federalreserve.gov/feeds/bankinginfo-rss.xml</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://www.federalreserve.gov/feeds/bankinginfo-rss.xml</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -521,7 +534,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="2" max="2" width="44.8984375" bestFit="1" customWidth="1"/>
@@ -529,201 +542,214 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="C1" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>3</v>
+        <v>44</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>2</v>
+        <v>45</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" t="s">
-        <v>27</v>
+        <v>4</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="C5" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>33</v>
+        <v>7</v>
+      </c>
+      <c r="C6" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C7" t="s">
-        <v>13</v>
+        <v>9</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>39</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>43</v>
+        <v>10</v>
+      </c>
+      <c r="B8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B9" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>41</v>
-      </c>
-      <c r="C9" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>34</v>
+        <v>39</v>
+      </c>
+      <c r="C10" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
+        <v>19</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B14" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C14" t="s">
-        <v>29</v>
+      <c r="C14" s="1" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" t="s">
+        <v>20</v>
+      </c>
+      <c r="B15" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B15" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="23" spans="5:5">
-      <c r="E23" s="1"/>
+      <c r="C15" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="24" spans="5:5">
+      <c r="E24" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <hyperlinks>
     <hyperlink ref="B1" r:id="rId1" display="https://www.federalreserve.gov/feeds/press_all.xml" xr:uid="{AD2ABE98-B33F-4FC8-8C7E-65C193CE41C5}"/>
-    <hyperlink ref="B2" r:id="rId2" display="https://www.fsb.org/wordpress/content_type/press/feed/" xr:uid="{65FA985E-12CB-4921-8FD9-E750F8E8A151}"/>
-    <hyperlink ref="B3" r:id="rId3" xr:uid="{D0F928E4-D44C-489B-926B-6BF42C6E2AB4}"/>
-    <hyperlink ref="B4" r:id="rId4" display="https://www.bis.org/doclist/all_pressrels.rss" xr:uid="{D57B539F-A6F0-4BE5-9AAE-BBDD08E7300C}"/>
-    <hyperlink ref="B5" r:id="rId5" display="https://www.bis.org/doclist/reshub_papers.rss" xr:uid="{7773DE6A-E2B9-4560-B83C-1C6D267FD16E}"/>
-    <hyperlink ref="B6" r:id="rId6" display="https://www.ecb.europa.eu/rss/press.html" xr:uid="{3D7C46ED-57D1-447D-A859-03AED8020C19}"/>
-    <hyperlink ref="B8" r:id="rId7" display="https://www.bankofengland.co.uk/rss/news" xr:uid="{209CE44D-5F38-4F84-84BF-93F2D800CC6D}"/>
-    <hyperlink ref="B10" r:id="rId8" display="https://www.srb.europa.eu/en/rss" xr:uid="{1483CF4B-34AE-4090-9D64-C5E56689A8C9}"/>
-    <hyperlink ref="B11" r:id="rId9" display="https://www.fsa.go.jp/fsaNewsListAll_rss2.xml" xr:uid="{0B345492-2480-4A66-A324-B646A6F1E0BE}"/>
-    <hyperlink ref="B12" r:id="rId10" display="https://www.boj.or.jp/rss/whatsnew.xml" xr:uid="{9448E3B6-904C-419A-8A4E-6B85A210121A}"/>
-    <hyperlink ref="B13" r:id="rId11" display="https://www.finma.ch/en/rss/news/" xr:uid="{A5BD1E52-3A1A-45CF-AE2B-DA7390C152AE}"/>
-    <hyperlink ref="B15" r:id="rId12" display="https://www.osfi-bsif.gc.ca/en/rss.xml" xr:uid="{CF34EFB6-8E03-484E-AF64-39FF66668F9B}"/>
-    <hyperlink ref="B14" r:id="rId13" display="https://www.hkma.gov.hk/eng/other-information/rss/rss_press-release.xml" xr:uid="{E6178445-FD71-43BA-9570-970C3ADB0968}"/>
+    <hyperlink ref="B3" r:id="rId2" display="https://www.fsb.org/wordpress/content_type/press/feed/" xr:uid="{65FA985E-12CB-4921-8FD9-E750F8E8A151}"/>
+    <hyperlink ref="B4" r:id="rId3" xr:uid="{D0F928E4-D44C-489B-926B-6BF42C6E2AB4}"/>
+    <hyperlink ref="B5" r:id="rId4" display="https://www.bis.org/doclist/all_pressrels.rss" xr:uid="{D57B539F-A6F0-4BE5-9AAE-BBDD08E7300C}"/>
+    <hyperlink ref="B6" r:id="rId5" display="https://www.bis.org/doclist/reshub_papers.rss" xr:uid="{7773DE6A-E2B9-4560-B83C-1C6D267FD16E}"/>
+    <hyperlink ref="B7" r:id="rId6" display="https://www.ecb.europa.eu/rss/press.html" xr:uid="{3D7C46ED-57D1-447D-A859-03AED8020C19}"/>
+    <hyperlink ref="B9" r:id="rId7" display="https://www.bankofengland.co.uk/rss/news" xr:uid="{209CE44D-5F38-4F84-84BF-93F2D800CC6D}"/>
+    <hyperlink ref="B11" r:id="rId8" display="https://www.srb.europa.eu/en/rss" xr:uid="{1483CF4B-34AE-4090-9D64-C5E56689A8C9}"/>
+    <hyperlink ref="B12" r:id="rId9" display="https://www.fsa.go.jp/fsaNewsListAll_rss2.xml" xr:uid="{0B345492-2480-4A66-A324-B646A6F1E0BE}"/>
+    <hyperlink ref="B13" r:id="rId10" display="https://www.boj.or.jp/rss/whatsnew.xml" xr:uid="{9448E3B6-904C-419A-8A4E-6B85A210121A}"/>
+    <hyperlink ref="B14" r:id="rId11" display="https://www.finma.ch/en/rss/news/" xr:uid="{A5BD1E52-3A1A-45CF-AE2B-DA7390C152AE}"/>
+    <hyperlink ref="B16" r:id="rId12" display="https://www.osfi-bsif.gc.ca/en/rss.xml" xr:uid="{CF34EFB6-8E03-484E-AF64-39FF66668F9B}"/>
+    <hyperlink ref="B15" r:id="rId13" display="https://www.hkma.gov.hk/eng/other-information/rss/rss_press-release.xml" xr:uid="{E6178445-FD71-43BA-9570-970C3ADB0968}"/>
     <hyperlink ref="C1" r:id="rId14" xr:uid="{26253DB1-109C-4BE7-9687-4B152716BD8F}"/>
-    <hyperlink ref="C2" r:id="rId15" xr:uid="{8327AE1A-7DAC-4947-B24A-A3C97BF238F5}"/>
-    <hyperlink ref="C3" r:id="rId16" xr:uid="{D2393C43-BE0D-4D32-A45B-A64D1D2B1680}"/>
-    <hyperlink ref="C6" r:id="rId17" xr:uid="{E28791F9-EC68-4ACE-BFA7-A943333207C5}"/>
-    <hyperlink ref="C10" r:id="rId18" xr:uid="{E7B21BD9-8195-4267-9254-C9BC4C4051AF}"/>
-    <hyperlink ref="C11" r:id="rId19" xr:uid="{169740BC-16C2-44CE-9E8D-69EC0B1C3F6D}"/>
-    <hyperlink ref="C12" r:id="rId20" xr:uid="{59E594E1-5460-47E4-8F37-F3F55D6740ED}"/>
-    <hyperlink ref="C13" r:id="rId21" xr:uid="{9590A641-5E0A-42AC-921B-1446080501C4}"/>
-    <hyperlink ref="C15" r:id="rId22" xr:uid="{D3FF31DC-FDCF-4A6E-8617-5241B9FFE395}"/>
-    <hyperlink ref="B9" r:id="rId23" display="https://www.bankofengland.co.uk/rss/publications" xr:uid="{428B6B0D-4299-47DC-A51C-997DC29E60B5}"/>
-    <hyperlink ref="C8" r:id="rId24" xr:uid="{80AF8D53-A9D0-4E6F-8EAF-4B6820D5436B}"/>
+    <hyperlink ref="C3" r:id="rId15" xr:uid="{8327AE1A-7DAC-4947-B24A-A3C97BF238F5}"/>
+    <hyperlink ref="C4" r:id="rId16" xr:uid="{D2393C43-BE0D-4D32-A45B-A64D1D2B1680}"/>
+    <hyperlink ref="C7" r:id="rId17" xr:uid="{E28791F9-EC68-4ACE-BFA7-A943333207C5}"/>
+    <hyperlink ref="C11" r:id="rId18" xr:uid="{E7B21BD9-8195-4267-9254-C9BC4C4051AF}"/>
+    <hyperlink ref="C12" r:id="rId19" xr:uid="{169740BC-16C2-44CE-9E8D-69EC0B1C3F6D}"/>
+    <hyperlink ref="C13" r:id="rId20" xr:uid="{59E594E1-5460-47E4-8F37-F3F55D6740ED}"/>
+    <hyperlink ref="C14" r:id="rId21" xr:uid="{9590A641-5E0A-42AC-921B-1446080501C4}"/>
+    <hyperlink ref="C16" r:id="rId22" xr:uid="{D3FF31DC-FDCF-4A6E-8617-5241B9FFE395}"/>
+    <hyperlink ref="B10" r:id="rId23" display="https://www.bankofengland.co.uk/rss/publications" xr:uid="{428B6B0D-4299-47DC-A51C-997DC29E60B5}"/>
+    <hyperlink ref="C9" r:id="rId24" xr:uid="{80AF8D53-A9D0-4E6F-8EAF-4B6820D5436B}"/>
+    <hyperlink ref="B2" r:id="rId25" display="https://www.federalreserve.gov/feeds/bankinginfo-rss.xml" xr:uid="{58045440-88B0-4F45-882C-BB4F703EA49D}"/>
+    <hyperlink ref="C2" r:id="rId26" xr:uid="{A5D591D1-E341-4E7F-903A-EFDE457F3486}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId25"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId27"/>
 </worksheet>
 </file>